--- a/excels/Semana_2026_06.xlsx
+++ b/excels/Semana_2026_06.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9abe27d133b37320/Temporal/Flujos de Pago/excels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\conta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="185" documentId="11_A28A860E899B08AE274A865D480D2EDAB32FDEF3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7069EDFC-4798-4A94-BA9D-CCF2C32B0ECB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99468E92-EE43-437C-9E81-60381ADAEA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1575" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Villas" sheetId="1" r:id="rId1"/>
     <sheet name="Pina" sheetId="2" r:id="rId2"/>
+    <sheet name="Villas In" sheetId="3" r:id="rId3"/>
+    <sheet name="Pina In" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="224">
   <si>
     <t>Fecha</t>
   </si>
@@ -679,13 +681,43 @@
   </si>
   <si>
     <t>Tecnología Extrema San Carlos Limitada OC 8498 (COMPRA DE 2 COMPUTADORAS PARA USO PREPARACION Y SEMILLA YS IEMBRA)</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Proyectado</t>
+  </si>
+  <si>
+    <t>Real</t>
+  </si>
+  <si>
+    <t>Deposito</t>
+  </si>
+  <si>
+    <t>Banco</t>
+  </si>
+  <si>
+    <t>Mayas</t>
+  </si>
+  <si>
+    <t>BCT</t>
+  </si>
+  <si>
+    <t>Pura Vida</t>
+  </si>
+  <si>
+    <t>BCR</t>
+  </si>
+  <si>
+    <t>Arjona</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -714,6 +746,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -735,7 +775,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -747,6 +787,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1190,7 +1234,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <f t="shared" ref="A2:A11" ca="1" si="0">TODAY()</f>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>164</v>
@@ -1208,7 +1252,7 @@
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>164</v>
@@ -1226,7 +1270,7 @@
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>164</v>
@@ -1244,7 +1288,7 @@
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>164</v>
@@ -1262,7 +1306,7 @@
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>164</v>
@@ -1280,7 +1324,7 @@
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>164</v>
@@ -1298,7 +1342,7 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>164</v>
@@ -1316,7 +1360,7 @@
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>164</v>
@@ -1334,7 +1378,7 @@
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>164</v>
@@ -1352,7 +1396,7 @@
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>164</v>
@@ -1368,7 +1412,7 @@
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <f ca="1">TODAY()</f>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>22</v>
@@ -1386,7 +1430,7 @@
     <row r="13" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <f t="shared" ref="A13:A76" ca="1" si="1">TODAY()</f>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>22</v>
@@ -1404,7 +1448,7 @@
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>22</v>
@@ -1422,7 +1466,7 @@
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>29</v>
@@ -1440,7 +1484,7 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>29</v>
@@ -1458,7 +1502,7 @@
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>29</v>
@@ -1476,7 +1520,7 @@
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>29</v>
@@ -1492,7 +1536,7 @@
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>29</v>
@@ -1510,7 +1554,7 @@
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>23</v>
@@ -1528,7 +1572,7 @@
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>23</v>
@@ -1544,7 +1588,7 @@
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>23</v>
@@ -1562,7 +1606,7 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>23</v>
@@ -1580,7 +1624,7 @@
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>23</v>
@@ -1596,7 +1640,7 @@
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>23</v>
@@ -1612,7 +1656,7 @@
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>30</v>
@@ -1630,7 +1674,7 @@
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B27" t="s">
         <v>30</v>
@@ -1648,7 +1692,7 @@
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B28" t="s">
         <v>30</v>
@@ -1666,7 +1710,7 @@
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B29" t="s">
         <v>31</v>
@@ -1684,7 +1728,7 @@
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
@@ -1702,7 +1746,7 @@
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
@@ -1717,7 +1761,7 @@
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B32" t="s">
         <v>31</v>
@@ -1732,7 +1776,7 @@
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B33" t="s">
         <v>32</v>
@@ -1750,7 +1794,7 @@
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B34" t="s">
         <v>33</v>
@@ -1768,7 +1812,7 @@
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B35" t="s">
         <v>33</v>
@@ -1786,7 +1830,7 @@
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B36" t="s">
         <v>33</v>
@@ -1804,7 +1848,7 @@
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B37" t="s">
         <v>19</v>
@@ -1822,7 +1866,7 @@
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B38" t="s">
         <v>19</v>
@@ -1840,7 +1884,7 @@
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B39" t="s">
         <v>34</v>
@@ -1858,7 +1902,7 @@
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B40" t="s">
         <v>34</v>
@@ -1876,7 +1920,7 @@
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B41" t="s">
         <v>35</v>
@@ -1891,7 +1935,7 @@
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B42" t="s">
         <v>35</v>
@@ -1906,7 +1950,7 @@
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B43" t="s">
         <v>35</v>
@@ -1921,7 +1965,7 @@
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B44" t="s">
         <v>35</v>
@@ -1936,7 +1980,7 @@
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B45" t="s">
         <v>36</v>
@@ -1954,7 +1998,7 @@
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B46" t="s">
         <v>36</v>
@@ -1972,7 +2016,7 @@
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B47" t="s">
         <v>37</v>
@@ -1990,7 +2034,7 @@
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B48" t="s">
         <v>37</v>
@@ -2008,7 +2052,7 @@
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B49" t="s">
         <v>37</v>
@@ -2026,7 +2070,7 @@
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B50" t="s">
         <v>37</v>
@@ -2044,7 +2088,7 @@
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B51" t="s">
         <v>8</v>
@@ -2062,7 +2106,7 @@
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B52" t="s">
         <v>8</v>
@@ -2080,7 +2124,7 @@
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B53" t="s">
         <v>8</v>
@@ -2098,7 +2142,7 @@
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B54" t="s">
         <v>8</v>
@@ -2116,7 +2160,7 @@
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B55" t="s">
         <v>8</v>
@@ -2134,7 +2178,7 @@
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B56" t="s">
         <v>8</v>
@@ -2152,7 +2196,7 @@
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B57" t="s">
         <v>38</v>
@@ -2170,7 +2214,7 @@
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B58" t="s">
         <v>39</v>
@@ -2185,7 +2229,7 @@
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B59" t="s">
         <v>40</v>
@@ -2200,7 +2244,7 @@
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B60" t="s">
         <v>40</v>
@@ -2215,7 +2259,7 @@
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B61" t="s">
         <v>41</v>
@@ -2233,7 +2277,7 @@
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B62" t="s">
         <v>41</v>
@@ -2248,7 +2292,7 @@
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B63" t="s">
         <v>25</v>
@@ -2266,7 +2310,7 @@
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B64" t="s">
         <v>25</v>
@@ -2284,7 +2328,7 @@
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B65" t="s">
         <v>25</v>
@@ -2302,7 +2346,7 @@
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B66" t="s">
         <v>25</v>
@@ -2320,7 +2364,7 @@
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B67" t="s">
         <v>25</v>
@@ -2338,7 +2382,7 @@
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B68" t="s">
         <v>25</v>
@@ -2356,7 +2400,7 @@
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B69" t="s">
         <v>25</v>
@@ -2374,7 +2418,7 @@
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B70" t="s">
         <v>25</v>
@@ -2392,7 +2436,7 @@
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B71" t="s">
         <v>25</v>
@@ -2410,7 +2454,7 @@
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B72" t="s">
         <v>25</v>
@@ -2428,7 +2472,7 @@
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B73" t="s">
         <v>25</v>
@@ -2446,7 +2490,7 @@
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B74" t="s">
         <v>25</v>
@@ -2464,7 +2508,7 @@
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B75" t="s">
         <v>25</v>
@@ -2482,7 +2526,7 @@
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B76" t="s">
         <v>25</v>
@@ -2500,7 +2544,7 @@
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <f t="shared" ref="A77:A140" ca="1" si="2">TODAY()</f>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B77" t="s">
         <v>25</v>
@@ -2515,7 +2559,7 @@
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B78" t="s">
         <v>25</v>
@@ -2530,7 +2574,7 @@
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B79" t="s">
         <v>25</v>
@@ -2545,7 +2589,7 @@
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B80" t="s">
         <v>25</v>
@@ -2560,7 +2604,7 @@
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B81" t="s">
         <v>9</v>
@@ -2575,7 +2619,7 @@
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B82" t="s">
         <v>9</v>
@@ -2590,7 +2634,7 @@
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B83" t="s">
         <v>9</v>
@@ -2605,7 +2649,7 @@
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B84" t="s">
         <v>42</v>
@@ -2623,7 +2667,7 @@
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B85" t="s">
         <v>42</v>
@@ -2638,7 +2682,7 @@
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B86" t="s">
         <v>43</v>
@@ -2656,7 +2700,7 @@
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B87" t="s">
         <v>43</v>
@@ -2674,7 +2718,7 @@
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B88" t="s">
         <v>43</v>
@@ -2692,7 +2736,7 @@
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B89" t="s">
         <v>43</v>
@@ -2710,7 +2754,7 @@
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B90" t="s">
         <v>43</v>
@@ -2728,7 +2772,7 @@
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B91" t="s">
         <v>43</v>
@@ -2746,7 +2790,7 @@
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B92" t="s">
         <v>43</v>
@@ -2764,7 +2808,7 @@
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B93" t="s">
         <v>43</v>
@@ -2782,7 +2826,7 @@
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B94" t="s">
         <v>43</v>
@@ -2800,7 +2844,7 @@
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B95" t="s">
         <v>43</v>
@@ -2818,7 +2862,7 @@
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B96" t="s">
         <v>43</v>
@@ -2836,7 +2880,7 @@
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B97" t="s">
         <v>43</v>
@@ -2854,7 +2898,7 @@
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B98" t="s">
         <v>43</v>
@@ -2872,7 +2916,7 @@
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B99" t="s">
         <v>43</v>
@@ -2890,7 +2934,7 @@
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B100" t="s">
         <v>43</v>
@@ -2908,7 +2952,7 @@
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B101" t="s">
         <v>43</v>
@@ -2926,7 +2970,7 @@
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B102" t="s">
         <v>43</v>
@@ -2944,7 +2988,7 @@
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B103" t="s">
         <v>43</v>
@@ -2962,7 +3006,7 @@
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B104" t="s">
         <v>43</v>
@@ -2980,7 +3024,7 @@
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B105" t="s">
         <v>43</v>
@@ -2998,7 +3042,7 @@
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B106" t="s">
         <v>43</v>
@@ -3016,7 +3060,7 @@
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B107" t="s">
         <v>43</v>
@@ -3034,7 +3078,7 @@
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B108" t="s">
         <v>43</v>
@@ -3049,7 +3093,7 @@
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B109" t="s">
         <v>43</v>
@@ -3064,7 +3108,7 @@
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B110" t="s">
         <v>43</v>
@@ -3079,7 +3123,7 @@
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B111" t="s">
         <v>43</v>
@@ -3094,7 +3138,7 @@
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B112" t="s">
         <v>43</v>
@@ -3109,7 +3153,7 @@
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B113" t="s">
         <v>43</v>
@@ -3124,7 +3168,7 @@
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B114" t="s">
         <v>43</v>
@@ -3139,7 +3183,7 @@
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B115" t="s">
         <v>43</v>
@@ -3154,7 +3198,7 @@
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B116" t="s">
         <v>43</v>
@@ -3169,7 +3213,7 @@
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B117" t="s">
         <v>43</v>
@@ -3184,7 +3228,7 @@
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B118" t="s">
         <v>43</v>
@@ -3199,7 +3243,7 @@
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B119" t="s">
         <v>43</v>
@@ -3214,7 +3258,7 @@
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B120" t="s">
         <v>43</v>
@@ -3229,7 +3273,7 @@
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B121" t="s">
         <v>43</v>
@@ -3244,7 +3288,7 @@
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B122" t="s">
         <v>43</v>
@@ -3259,7 +3303,7 @@
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B123" t="s">
         <v>43</v>
@@ -3274,7 +3318,7 @@
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B124" t="s">
         <v>43</v>
@@ -3289,7 +3333,7 @@
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B125" t="s">
         <v>43</v>
@@ -3304,7 +3348,7 @@
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B126" t="s">
         <v>43</v>
@@ -3319,7 +3363,7 @@
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B127" t="s">
         <v>43</v>
@@ -3334,7 +3378,7 @@
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B128" t="s">
         <v>43</v>
@@ -3349,7 +3393,7 @@
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B129" t="s">
         <v>43</v>
@@ -3364,7 +3408,7 @@
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B130" t="s">
         <v>43</v>
@@ -3379,7 +3423,7 @@
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B131" t="s">
         <v>43</v>
@@ -3394,7 +3438,7 @@
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B132" t="s">
         <v>43</v>
@@ -3409,7 +3453,7 @@
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B133" t="s">
         <v>43</v>
@@ -3424,7 +3468,7 @@
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B134" t="s">
         <v>43</v>
@@ -3439,7 +3483,7 @@
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B135" t="s">
         <v>43</v>
@@ -3454,7 +3498,7 @@
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B136" t="s">
         <v>43</v>
@@ -3469,7 +3513,7 @@
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B137" t="s">
         <v>43</v>
@@ -3484,7 +3528,7 @@
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B138" t="s">
         <v>43</v>
@@ -3499,7 +3543,7 @@
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B139" t="s">
         <v>43</v>
@@ -3514,7 +3558,7 @@
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <f t="shared" ca="1" si="2"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B140" t="s">
         <v>43</v>
@@ -3529,7 +3573,7 @@
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <f t="shared" ref="A141:A204" ca="1" si="3">TODAY()</f>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B141" t="s">
         <v>43</v>
@@ -3544,7 +3588,7 @@
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B142" t="s">
         <v>43</v>
@@ -3559,7 +3603,7 @@
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B143" t="s">
         <v>43</v>
@@ -3574,7 +3618,7 @@
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B144" t="s">
         <v>43</v>
@@ -3589,7 +3633,7 @@
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B145" t="s">
         <v>24</v>
@@ -3607,7 +3651,7 @@
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B146" t="s">
         <v>24</v>
@@ -3625,7 +3669,7 @@
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B147" t="s">
         <v>24</v>
@@ -3640,7 +3684,7 @@
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B148" t="s">
         <v>24</v>
@@ -3658,7 +3702,7 @@
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B149" t="s">
         <v>24</v>
@@ -3676,7 +3720,7 @@
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B150" t="s">
         <v>24</v>
@@ -3691,7 +3735,7 @@
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B151" t="s">
         <v>44</v>
@@ -3709,7 +3753,7 @@
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="s">
         <v>44</v>
@@ -3727,7 +3771,7 @@
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B153" t="s">
         <v>44</v>
@@ -3745,7 +3789,7 @@
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B154" t="s">
         <v>44</v>
@@ -3763,7 +3807,7 @@
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B155" t="s">
         <v>44</v>
@@ -3781,7 +3825,7 @@
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B156" t="s">
         <v>44</v>
@@ -3799,7 +3843,7 @@
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B157" t="s">
         <v>44</v>
@@ -3817,7 +3861,7 @@
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B158" t="s">
         <v>44</v>
@@ -3835,7 +3879,7 @@
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B159" t="s">
         <v>44</v>
@@ -3853,7 +3897,7 @@
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B160" t="s">
         <v>44</v>
@@ -3871,7 +3915,7 @@
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B161" t="s">
         <v>44</v>
@@ -3889,7 +3933,7 @@
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B162" t="s">
         <v>44</v>
@@ -3907,7 +3951,7 @@
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B163" t="s">
         <v>45</v>
@@ -3925,7 +3969,7 @@
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B164" t="s">
         <v>45</v>
@@ -3943,7 +3987,7 @@
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B165" t="s">
         <v>45</v>
@@ -3961,7 +4005,7 @@
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B166" t="s">
         <v>45</v>
@@ -3979,7 +4023,7 @@
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B167" t="s">
         <v>45</v>
@@ -3997,7 +4041,7 @@
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B168" t="s">
         <v>45</v>
@@ -4015,7 +4059,7 @@
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B169" t="s">
         <v>45</v>
@@ -4033,7 +4077,7 @@
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B170" t="s">
         <v>45</v>
@@ -4051,7 +4095,7 @@
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B171" t="s">
         <v>45</v>
@@ -4069,7 +4113,7 @@
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B172" t="s">
         <v>45</v>
@@ -4087,7 +4131,7 @@
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B173" t="s">
         <v>45</v>
@@ -4105,7 +4149,7 @@
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B174" t="s">
         <v>45</v>
@@ -4123,7 +4167,7 @@
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B175" t="s">
         <v>45</v>
@@ -4141,7 +4185,7 @@
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B176" t="s">
         <v>28</v>
@@ -4159,7 +4203,7 @@
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B177" t="s">
         <v>28</v>
@@ -4177,7 +4221,7 @@
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B178" t="s">
         <v>28</v>
@@ -4195,7 +4239,7 @@
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B179" t="s">
         <v>28</v>
@@ -4213,7 +4257,7 @@
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B180" t="s">
         <v>28</v>
@@ -4231,7 +4275,7 @@
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B181" t="s">
         <v>28</v>
@@ -4249,7 +4293,7 @@
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B182" t="s">
         <v>28</v>
@@ -4267,7 +4311,7 @@
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B183" t="s">
         <v>28</v>
@@ -4285,7 +4329,7 @@
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B184" t="s">
         <v>28</v>
@@ -4303,7 +4347,7 @@
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B185" t="s">
         <v>28</v>
@@ -4321,7 +4365,7 @@
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B186" t="s">
         <v>28</v>
@@ -4339,7 +4383,7 @@
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B187" t="s">
         <v>28</v>
@@ -4357,7 +4401,7 @@
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B188" t="s">
         <v>28</v>
@@ -4375,7 +4419,7 @@
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B189" t="s">
         <v>28</v>
@@ -4393,7 +4437,7 @@
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B190" t="s">
         <v>27</v>
@@ -4411,7 +4455,7 @@
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B191" t="s">
         <v>27</v>
@@ -4429,7 +4473,7 @@
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B192" t="s">
         <v>27</v>
@@ -4447,7 +4491,7 @@
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B193" t="s">
         <v>27</v>
@@ -4465,7 +4509,7 @@
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B194" t="s">
         <v>27</v>
@@ -4483,7 +4527,7 @@
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B195" t="s">
         <v>27</v>
@@ -4501,7 +4545,7 @@
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B196" t="s">
         <v>27</v>
@@ -4519,7 +4563,7 @@
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B197" t="s">
         <v>27</v>
@@ -4537,7 +4581,7 @@
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B198" t="s">
         <v>27</v>
@@ -4555,7 +4599,7 @@
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B199" t="s">
         <v>27</v>
@@ -4573,7 +4617,7 @@
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B200" t="s">
         <v>27</v>
@@ -4591,7 +4635,7 @@
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B201" t="s">
         <v>27</v>
@@ -4609,7 +4653,7 @@
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B202" t="s">
         <v>27</v>
@@ -4627,7 +4671,7 @@
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B203" t="s">
         <v>46</v>
@@ -4642,7 +4686,7 @@
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <f t="shared" ca="1" si="3"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B204" t="s">
         <v>46</v>
@@ -4657,7 +4701,7 @@
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <f t="shared" ref="A205:A230" ca="1" si="4">TODAY()</f>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B205" t="s">
         <v>47</v>
@@ -4675,7 +4719,7 @@
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B206" t="s">
         <v>48</v>
@@ -4693,7 +4737,7 @@
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B207" t="s">
         <v>48</v>
@@ -4711,7 +4755,7 @@
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B208" t="s">
         <v>48</v>
@@ -4729,7 +4773,7 @@
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B209" t="s">
         <v>48</v>
@@ -4747,7 +4791,7 @@
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B210" t="s">
         <v>49</v>
@@ -4765,7 +4809,7 @@
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B211" t="s">
         <v>49</v>
@@ -4783,7 +4827,7 @@
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B212" t="s">
         <v>49</v>
@@ -4801,7 +4845,7 @@
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B213" t="s">
         <v>49</v>
@@ -4816,7 +4860,7 @@
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B214" t="s">
         <v>50</v>
@@ -4831,7 +4875,7 @@
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B215" t="s">
         <v>50</v>
@@ -4846,7 +4890,7 @@
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B216" t="s">
         <v>51</v>
@@ -4861,7 +4905,7 @@
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B217" t="s">
         <v>51</v>
@@ -4879,7 +4923,7 @@
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B218" t="s">
         <v>52</v>
@@ -4897,7 +4941,7 @@
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B219" t="s">
         <v>52</v>
@@ -4915,7 +4959,7 @@
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B220" t="s">
         <v>52</v>
@@ -4933,7 +4977,7 @@
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B221" t="s">
         <v>26</v>
@@ -4951,7 +4995,7 @@
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B222" t="s">
         <v>26</v>
@@ -4969,7 +5013,7 @@
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B223" t="s">
         <v>26</v>
@@ -4984,7 +5028,7 @@
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B224" t="s">
         <v>26</v>
@@ -5002,7 +5046,7 @@
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B225" t="s">
         <v>26</v>
@@ -5020,7 +5064,7 @@
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B226" t="s">
         <v>26</v>
@@ -5038,7 +5082,7 @@
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B227" t="s">
         <v>53</v>
@@ -5056,7 +5100,7 @@
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B228" t="s">
         <v>53</v>
@@ -5074,7 +5118,7 @@
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B229" t="s">
         <v>54</v>
@@ -5092,7 +5136,7 @@
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <f t="shared" ca="1" si="4"/>
-        <v>46059</v>
+        <v>46132</v>
       </c>
       <c r="B230" t="s">
         <v>54</v>
@@ -5111,4 +5155,124 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D4F033-3166-4DD3-90C5-BF92621DFBDF}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F2489B-E149-4E4A-8099-902CD7EBE730}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2">
+        <v>59000</v>
+      </c>
+      <c r="C2">
+        <v>39000</v>
+      </c>
+      <c r="D2" s="5">
+        <v>46127</v>
+      </c>
+      <c r="E2">
+        <v>1112253</v>
+      </c>
+      <c r="F2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3">
+        <v>15000</v>
+      </c>
+      <c r="C3">
+        <v>10000</v>
+      </c>
+      <c r="D3" s="5">
+        <v>46126</v>
+      </c>
+      <c r="E3">
+        <v>1112344</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4">
+        <v>25000</v>
+      </c>
+      <c r="C4">
+        <v>25000</v>
+      </c>
+      <c r="D4" s="5">
+        <v>46127</v>
+      </c>
+      <c r="E4">
+        <v>223465</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>